--- a/Dependencies/Ping_2018/acg/dataset_metrics.xlsx
+++ b/Dependencies/Ping_2018/acg/dataset_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118301</v>
+        <v>112553</v>
       </c>
       <c r="C2" t="n">
-        <v>73189</v>
+        <v>71335</v>
       </c>
       <c r="D2" t="n">
-        <v>73026</v>
+        <v>71227</v>
       </c>
       <c r="E2" t="n">
-        <v>13846</v>
+        <v>13529</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>101640</v>
+        <v>103223</v>
       </c>
       <c r="C3" t="n">
-        <v>68830</v>
+        <v>71720</v>
       </c>
       <c r="D3" t="n">
-        <v>68677</v>
+        <v>71592</v>
       </c>
       <c r="E3" t="n">
-        <v>13185</v>
+        <v>13787</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106532</v>
+        <v>101486</v>
       </c>
       <c r="C4" t="n">
-        <v>73986</v>
+        <v>72031</v>
       </c>
       <c r="D4" t="n">
-        <v>73817</v>
+        <v>71902</v>
       </c>
       <c r="E4" t="n">
-        <v>14236</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86649</v>
+        <v>83609</v>
       </c>
       <c r="C5" t="n">
-        <v>61420</v>
+        <v>60342</v>
       </c>
       <c r="D5" t="n">
-        <v>61298</v>
+        <v>60256</v>
       </c>
       <c r="E5" t="n">
-        <v>11519</v>
+        <v>11303</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92441</v>
+        <v>91758</v>
       </c>
       <c r="C6" t="n">
-        <v>66337</v>
+        <v>65912</v>
       </c>
       <c r="D6" t="n">
-        <v>66192</v>
+        <v>65777</v>
       </c>
       <c r="E6" t="n">
-        <v>12589</v>
+        <v>12519</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/acg/dataset_metrics.xlsx
+++ b/Dependencies/Ping_2018/acg/dataset_metrics.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112553</v>
+        <v>209933</v>
       </c>
       <c r="C2" t="n">
-        <v>71335</v>
+        <v>90703</v>
       </c>
       <c r="D2" t="n">
-        <v>71227</v>
+        <v>90703</v>
       </c>
       <c r="E2" t="n">
-        <v>13529</v>
+        <v>17574</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103223</v>
+        <v>195200</v>
       </c>
       <c r="C3" t="n">
-        <v>71720</v>
+        <v>91495</v>
       </c>
       <c r="D3" t="n">
-        <v>71592</v>
+        <v>91495</v>
       </c>
       <c r="E3" t="n">
-        <v>13787</v>
+        <v>17942</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101486</v>
+        <v>200265</v>
       </c>
       <c r="C4" t="n">
-        <v>72031</v>
+        <v>94334</v>
       </c>
       <c r="D4" t="n">
-        <v>71902</v>
+        <v>94334</v>
       </c>
       <c r="E4" t="n">
-        <v>13840</v>
+        <v>18435</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83609</v>
+        <v>202734</v>
       </c>
       <c r="C5" t="n">
-        <v>60342</v>
+        <v>88983</v>
       </c>
       <c r="D5" t="n">
-        <v>60256</v>
+        <v>88983</v>
       </c>
       <c r="E5" t="n">
-        <v>11303</v>
+        <v>17259</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>194238</v>
       </c>
       <c r="C6" t="n">
-        <v>65912</v>
+        <v>89149</v>
       </c>
       <c r="D6" t="n">
-        <v>65777</v>
+        <v>89149</v>
       </c>
       <c r="E6" t="n">
-        <v>12519</v>
+        <v>17389</v>
       </c>
     </row>
   </sheetData>
